--- a/data/trans_orig/IP1013-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Habitat-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149858</t>
+          <t>149677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288653</t>
+          <t>288598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191321</t>
+          <t>190762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402312</t>
+          <t>402897</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>676593</t>
+          <t>677199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>719324</t>
+          <t>718659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397984</t>
+          <t>1398516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133257</t>
+          <t>132578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149646</t>
+          <t>148997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284834</t>
+          <t>284767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201987</t>
+          <t>201988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218160</t>
+          <t>218647</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>422615</t>
+          <t>422658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206655</t>
+          <t>205878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203945</t>
+          <t>203416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412219</t>
+          <t>412687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701128</t>
+          <t>701139</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>706269</t>
+          <t>706272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742487</t>
+          <t>742835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747517</t>
+          <t>747518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1446765</t>
+          <t>1446288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453706</t>
+          <t>1453093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129772</t>
+          <t>128468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277861</t>
+          <t>277899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202579</t>
+          <t>202818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408837</t>
+          <t>408927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5998,54 +5998,54 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5993</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5306</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>699065</t>
+          <t>698378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>704371</t>
+          <t>703774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,39 +6126,39 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443483</t>
+          <t>1443560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1013-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4269</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152404</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>148808</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152404</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149677</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288598</t>
+          <t>288098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4401</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3812</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4446</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4408</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>193899</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>190762</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191351</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>632</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402897</t>
+          <t>402859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3375</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3822</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4443</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>722027</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>719325</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679757</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>677199</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>676578</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>722027</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>718659</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2101</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1398516</t>
+          <t>1398333</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1403100</t>
+          <t>1403096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2674,102 +2674,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3509</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3813</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4134</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1348</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152411</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149589</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135730</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>132578</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>133063</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152411</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>148997</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>392</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284767</t>
+          <t>285355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3017,102 +3017,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>685</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3410</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3445</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3330</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4736</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4718</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221309</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>218610</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204713</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>201988</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>201953</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221309</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>218647</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>636</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>422658</t>
+          <t>422640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3468,47 +3468,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3703,102 +3703,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4422</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4122</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3666</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4915</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206458</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>204259</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209569</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>205878</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>206178</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206458</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203416</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>554</t>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412687</t>
+          <t>412467</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2076</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5789</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5725</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746163</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>742841</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>747519</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704852</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>701139</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>706272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>701203</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>706268</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>746163</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>742835</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>747518</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2078</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1446288</t>
+          <t>1446498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453093</t>
+          <t>1453716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5239</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4277</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3884</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>132936</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>128468</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130089</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>381</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277899</t>
+          <t>277506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5072,47 +5072,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1302</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4602</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4733</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4229</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>206118</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>202818</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>202687</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>569</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408927</t>
+          <t>408653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5993</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>702297</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698378</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698272</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>703774</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2123</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443560</t>
+          <t>1443340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448618</t>
+          <t>1448619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
